--- a/GIS2/parcely_gps.xlsx
+++ b/GIS2/parcely_gps.xlsx
@@ -40,10 +40,10 @@
     <t>Chodov</t>
   </si>
   <si>
-    <t>1358/2</t>
-  </si>
-  <si>
-    <t>2031/391</t>
+    <t>1199/19</t>
+  </si>
+  <si>
+    <t>2031/390</t>
   </si>
 </sst>
 </file>
@@ -438,10 +438,10 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <v>50.03051123</v>
+        <v>50.02946672</v>
       </c>
       <c r="F2">
-        <v>14.50574804</v>
+        <v>14.50618033</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -458,10 +458,10 @@
         <v>9</v>
       </c>
       <c r="E3">
-        <v>50.02861446</v>
+        <v>50.02919452</v>
       </c>
       <c r="F3">
-        <v>14.50615477</v>
+        <v>14.50616319</v>
       </c>
     </row>
   </sheetData>

--- a/GIS2/parcely_gps.xlsx
+++ b/GIS2/parcely_gps.xlsx
@@ -34,16 +34,16 @@
     <t>lon</t>
   </si>
   <si>
-    <t>Praha</t>
-  </si>
-  <si>
-    <t>Chodov</t>
-  </si>
-  <si>
-    <t>1199/19</t>
-  </si>
-  <si>
-    <t>2031/390</t>
+    <t>Nymburk</t>
+  </si>
+  <si>
+    <t>Mcely</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>919/5</t>
   </si>
 </sst>
 </file>
@@ -432,16 +432,16 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
       </c>
       <c r="E2">
-        <v>50.02946672</v>
+        <v>50.30324114</v>
       </c>
       <c r="F2">
-        <v>14.50618033</v>
+        <v>15.07640251</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -452,16 +452,16 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
       <c r="E3">
-        <v>50.02919452</v>
+        <v>50.30516456</v>
       </c>
       <c r="F3">
-        <v>14.50616319</v>
+        <v>15.07559649</v>
       </c>
     </row>
   </sheetData>

--- a/GIS2/parcely_gps.xlsx
+++ b/GIS2/parcely_gps.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="47">
   <si>
     <t>okres</t>
   </si>
@@ -28,22 +28,133 @@
     <t>parcelni_cislo</t>
   </si>
   <si>
+    <t>LV</t>
+  </si>
+  <si>
     <t>lat</t>
   </si>
   <si>
     <t>lon</t>
   </si>
   <si>
-    <t>Nymburk</t>
-  </si>
-  <si>
-    <t>Mcely</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>919/5</t>
+    <t>Praha</t>
+  </si>
+  <si>
+    <t>Újezd u Průhonic</t>
+  </si>
+  <si>
+    <t>Šeberov</t>
+  </si>
+  <si>
+    <t>Křeslice</t>
+  </si>
+  <si>
+    <t>213/14</t>
+  </si>
+  <si>
+    <t>213/19</t>
+  </si>
+  <si>
+    <t>213/21</t>
+  </si>
+  <si>
+    <t>214/17</t>
+  </si>
+  <si>
+    <t>214/18</t>
+  </si>
+  <si>
+    <t>214/21</t>
+  </si>
+  <si>
+    <t>214/37</t>
+  </si>
+  <si>
+    <t>214/38</t>
+  </si>
+  <si>
+    <t>214/43</t>
+  </si>
+  <si>
+    <t>214/69</t>
+  </si>
+  <si>
+    <t>214/207</t>
+  </si>
+  <si>
+    <t>214/502</t>
+  </si>
+  <si>
+    <t>213/17</t>
+  </si>
+  <si>
+    <t>213/18</t>
+  </si>
+  <si>
+    <t>213/24</t>
+  </si>
+  <si>
+    <t>214/36</t>
+  </si>
+  <si>
+    <t>214/51</t>
+  </si>
+  <si>
+    <t>214/59</t>
+  </si>
+  <si>
+    <t>214/66</t>
+  </si>
+  <si>
+    <t>214/67</t>
+  </si>
+  <si>
+    <t>214/80</t>
+  </si>
+  <si>
+    <t>214/81</t>
+  </si>
+  <si>
+    <t>214/82</t>
+  </si>
+  <si>
+    <t>214/83</t>
+  </si>
+  <si>
+    <t>214/84</t>
+  </si>
+  <si>
+    <t>214/503</t>
+  </si>
+  <si>
+    <t>626/12</t>
+  </si>
+  <si>
+    <t>674/5</t>
+  </si>
+  <si>
+    <t>537/14</t>
+  </si>
+  <si>
+    <t>537/28</t>
+  </si>
+  <si>
+    <t>413/18</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>544</t>
+  </si>
+  <si>
+    <t>813</t>
+  </si>
+  <si>
+    <t>812</t>
+  </si>
+  <si>
+    <t>72</t>
   </si>
 </sst>
 </file>
@@ -401,10 +512,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -423,45 +534,721 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2">
-        <v>50.30324114</v>
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>42</v>
       </c>
       <c r="F2">
-        <v>15.07640251</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>50.01654768</v>
+      </c>
+      <c r="G2">
+        <v>14.53134025</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3">
+        <v>50.01610456</v>
+      </c>
+      <c r="G3">
+        <v>14.53512725</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4">
+        <v>50.0158859</v>
+      </c>
+      <c r="G4">
+        <v>14.53690793</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5">
+        <v>50.01300854</v>
+      </c>
+      <c r="G5">
+        <v>14.53492734</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6">
+        <v>50.01478244</v>
+      </c>
+      <c r="G6">
+        <v>14.53202983</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7">
+        <v>50.01520949</v>
+      </c>
+      <c r="G7">
+        <v>14.5302806</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8">
+        <v>50.01499042</v>
+      </c>
+      <c r="G8">
+        <v>14.52843607</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9">
+        <v>50.0149388</v>
+      </c>
+      <c r="G9">
+        <v>14.5288262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10">
+        <v>50.01287541</v>
+      </c>
+      <c r="G10">
+        <v>14.53679955</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11">
+        <v>50.01454711</v>
+      </c>
+      <c r="G11">
+        <v>14.53618752</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12">
+        <v>50.01593787</v>
+      </c>
+      <c r="G12">
+        <v>14.53032712</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13">
+        <v>50.01377384</v>
+      </c>
+      <c r="G13">
+        <v>14.53431865</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14">
+        <v>50.01628422</v>
+      </c>
+      <c r="G14">
+        <v>14.53358108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15">
+        <v>50.01618908</v>
+      </c>
+      <c r="G15">
+        <v>14.534395</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16">
+        <v>50.01632259</v>
+      </c>
+      <c r="G16">
+        <v>14.53323936</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17">
+        <v>50.01516677</v>
+      </c>
+      <c r="G17">
+        <v>14.52841063</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18">
+        <v>50.01243992</v>
+      </c>
+      <c r="G18">
+        <v>14.53915335</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19">
+        <v>50.01197576</v>
+      </c>
+      <c r="G19">
+        <v>14.53916654</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20">
+        <v>50.01331552</v>
+      </c>
+      <c r="G20">
+        <v>14.53353448</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21">
+        <v>50.01497798</v>
+      </c>
+      <c r="G21">
+        <v>14.53436939</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22">
+        <v>50.01508586</v>
+      </c>
+      <c r="G22">
+        <v>14.5332444</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23">
+        <v>50.01602229</v>
+      </c>
+      <c r="G23">
+        <v>14.53355669</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24">
+        <v>50.01516762</v>
+      </c>
+      <c r="G24">
+        <v>14.53355384</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25">
+        <v>50.01439714</v>
+      </c>
+      <c r="G25">
+        <v>14.53356221</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26">
+        <v>50.01367488</v>
+      </c>
+      <c r="G26">
+        <v>14.53347577</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27">
+        <v>50.01582172</v>
+      </c>
+      <c r="G27">
+        <v>14.53432415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28">
+        <v>50.01117134</v>
+      </c>
+      <c r="G28">
+        <v>14.54012006</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29">
+        <v>50.01620961</v>
+      </c>
+      <c r="G29">
+        <v>14.54602403</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
         <v>9</v>
       </c>
-      <c r="E3">
-        <v>50.30516456</v>
-      </c>
-      <c r="F3">
-        <v>15.07559649</v>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30">
+        <v>50.01342136</v>
+      </c>
+      <c r="G30">
+        <v>14.53087069</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31">
+        <v>50.01481945</v>
+      </c>
+      <c r="G31">
+        <v>14.52736139</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32">
+        <v>50.02282062</v>
+      </c>
+      <c r="G32">
+        <v>14.55170546</v>
       </c>
     </row>
   </sheetData>

--- a/GIS2/parcely_gps.xlsx
+++ b/GIS2/parcely_gps.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="40">
   <si>
     <t>okres</t>
   </si>
@@ -43,67 +43,97 @@
     <t>Praha</t>
   </si>
   <si>
-    <t>Hostivař</t>
-  </si>
-  <si>
-    <t>Strašnice</t>
-  </si>
-  <si>
-    <t>1714/4</t>
-  </si>
-  <si>
-    <t>1714/5</t>
-  </si>
-  <si>
-    <t>1714/6</t>
-  </si>
-  <si>
-    <t>1714/7</t>
-  </si>
-  <si>
-    <t>1714/8</t>
-  </si>
-  <si>
-    <t>1714/3</t>
-  </si>
-  <si>
-    <t>4241/9</t>
-  </si>
-  <si>
-    <t>4174/1</t>
-  </si>
-  <si>
-    <t>2648/1</t>
-  </si>
-  <si>
-    <t>4302/235</t>
-  </si>
-  <si>
-    <t>1594</t>
-  </si>
-  <si>
-    <t>804</t>
-  </si>
-  <si>
-    <t>x1</t>
-  </si>
-  <si>
-    <t>x3</t>
-  </si>
-  <si>
-    <t>x4</t>
-  </si>
-  <si>
-    <t>x5</t>
-  </si>
-  <si>
-    <t>Historicky oceňované další pozemky ZP 1300-15-2009, Ing.Arch. Soukeník</t>
-  </si>
-  <si>
-    <t>Oceňovaný pozemek</t>
-  </si>
-  <si>
-    <t>Test pozemek s cenou</t>
+    <t>Karlín</t>
+  </si>
+  <si>
+    <t>693/245</t>
+  </si>
+  <si>
+    <t>693/159</t>
+  </si>
+  <si>
+    <t>693/246</t>
+  </si>
+  <si>
+    <t>693/222</t>
+  </si>
+  <si>
+    <t>693/182</t>
+  </si>
+  <si>
+    <t>693/221</t>
+  </si>
+  <si>
+    <t>693/233</t>
+  </si>
+  <si>
+    <t>693/223</t>
+  </si>
+  <si>
+    <t>693/224</t>
+  </si>
+  <si>
+    <t>693/183</t>
+  </si>
+  <si>
+    <t>693/230</t>
+  </si>
+  <si>
+    <t>693/226</t>
+  </si>
+  <si>
+    <t>693/227</t>
+  </si>
+  <si>
+    <t>693/185</t>
+  </si>
+  <si>
+    <t>693/184</t>
+  </si>
+  <si>
+    <t>693/225</t>
+  </si>
+  <si>
+    <t>693/228</t>
+  </si>
+  <si>
+    <t>693/229</t>
+  </si>
+  <si>
+    <t>693/186</t>
+  </si>
+  <si>
+    <t>693/74</t>
+  </si>
+  <si>
+    <t>693/158</t>
+  </si>
+  <si>
+    <t>693/157</t>
+  </si>
+  <si>
+    <t>693/75</t>
+  </si>
+  <si>
+    <t>693/163</t>
+  </si>
+  <si>
+    <t>693/141</t>
+  </si>
+  <si>
+    <t>693/76</t>
+  </si>
+  <si>
+    <t>693/190</t>
+  </si>
+  <si>
+    <t>693/140</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>NOVÁ INVALIDOVNA - Novostavba dvou bytových domů a ubytovacího objektu</t>
   </si>
 </sst>
 </file>
@@ -461,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -501,19 +531,19 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>50.06650549</v>
+        <v>50.09685859</v>
       </c>
       <c r="H2">
-        <v>14.52198678</v>
+        <v>14.46331886</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -527,19 +557,19 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>50.06669548</v>
+        <v>50.09707398</v>
       </c>
       <c r="H3">
-        <v>14.52197194</v>
+        <v>14.46374658</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -553,19 +583,19 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G4">
-        <v>50.06661876</v>
+        <v>50.09690494</v>
       </c>
       <c r="H4">
-        <v>14.52232327</v>
+        <v>14.46390335</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -579,19 +609,19 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>50.06681047</v>
+        <v>50.09719019</v>
       </c>
       <c r="H5">
-        <v>14.5223178</v>
+        <v>14.46392314</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -605,19 +635,19 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G6">
-        <v>50.06654328</v>
+        <v>50.09718533</v>
       </c>
       <c r="H6">
-        <v>14.52292063</v>
+        <v>14.46416345</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -631,19 +661,19 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G7">
-        <v>50.06508036</v>
+        <v>50.09698222</v>
       </c>
       <c r="H7">
-        <v>14.52194416</v>
+        <v>14.46419218</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -651,25 +681,25 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G8">
-        <v>50.06742595</v>
+        <v>50.09698781</v>
       </c>
       <c r="H8">
-        <v>14.51515302</v>
+        <v>14.46421554</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -677,25 +707,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G9">
-        <v>50.06727126</v>
+        <v>50.09708465</v>
       </c>
       <c r="H9">
-        <v>14.51659288</v>
+        <v>14.46442557</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -709,19 +739,19 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G10">
-        <v>50.06262521</v>
+        <v>50.09702665</v>
       </c>
       <c r="H10">
-        <v>14.52141416</v>
+        <v>14.4644636</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -729,25 +759,493 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11">
+        <v>50.09737867</v>
+      </c>
+      <c r="H11">
+        <v>14.46432457</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
         <v>20</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12">
+        <v>50.09745444</v>
+      </c>
+      <c r="H12">
+        <v>14.46450778</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13">
+        <v>50.09738917</v>
+      </c>
+      <c r="H13">
+        <v>14.46447146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14">
+        <v>50.09720569</v>
+      </c>
+      <c r="H14">
+        <v>14.4645633</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15">
+        <v>50.09728172</v>
+      </c>
+      <c r="H15">
+        <v>14.46465263</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16">
+        <v>50.09750857</v>
+      </c>
+      <c r="H16">
+        <v>14.46466371</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17">
+        <v>50.09745628</v>
+      </c>
+      <c r="H17">
+        <v>14.46470363</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" t="s">
         <v>26</v>
       </c>
-      <c r="F11" t="s">
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18">
+        <v>50.09742068</v>
+      </c>
+      <c r="H18">
+        <v>14.46469611</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19">
+        <v>50.09728398</v>
+      </c>
+      <c r="H19">
+        <v>14.46476276</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20">
+        <v>50.09716693</v>
+      </c>
+      <c r="H20">
+        <v>14.46502555</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
         <v>29</v>
       </c>
-      <c r="G11">
-        <v>50.06269335</v>
-      </c>
-      <c r="H11">
-        <v>14.51749053</v>
+      <c r="E21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21">
+        <v>50.0973429</v>
+      </c>
+      <c r="H21">
+        <v>14.46493389</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22">
+        <v>50.09753611</v>
+      </c>
+      <c r="H22">
+        <v>14.46483405</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23">
+        <v>50.09761448</v>
+      </c>
+      <c r="H23">
+        <v>14.46507977</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24">
+        <v>50.09741135</v>
+      </c>
+      <c r="H24">
+        <v>14.46518652</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25">
+        <v>50.09687911</v>
+      </c>
+      <c r="H25">
+        <v>14.46568813</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26">
+        <v>50.09769743</v>
+      </c>
+      <c r="H26">
+        <v>14.46539688</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27">
+        <v>50.09746924</v>
+      </c>
+      <c r="H27">
+        <v>14.46552519</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28">
+        <v>50.09737217</v>
+      </c>
+      <c r="H28">
+        <v>14.46591578</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29">
+        <v>50.09750687</v>
+      </c>
+      <c r="H29">
+        <v>14.46583574</v>
       </c>
     </row>
   </sheetData>

--- a/GIS2/parcely_gps.xlsx
+++ b/GIS2/parcely_gps.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="49">
   <si>
     <t>okres</t>
   </si>
@@ -43,97 +43,124 @@
     <t>Praha</t>
   </si>
   <si>
-    <t>Karlín</t>
-  </si>
-  <si>
-    <t>693/245</t>
-  </si>
-  <si>
-    <t>693/159</t>
-  </si>
-  <si>
-    <t>693/246</t>
-  </si>
-  <si>
-    <t>693/222</t>
-  </si>
-  <si>
-    <t>693/182</t>
-  </si>
-  <si>
-    <t>693/221</t>
-  </si>
-  <si>
-    <t>693/233</t>
-  </si>
-  <si>
-    <t>693/223</t>
-  </si>
-  <si>
-    <t>693/224</t>
-  </si>
-  <si>
-    <t>693/183</t>
-  </si>
-  <si>
-    <t>693/230</t>
-  </si>
-  <si>
-    <t>693/226</t>
-  </si>
-  <si>
-    <t>693/227</t>
-  </si>
-  <si>
-    <t>693/185</t>
-  </si>
-  <si>
-    <t>693/184</t>
-  </si>
-  <si>
-    <t>693/225</t>
-  </si>
-  <si>
-    <t>693/228</t>
-  </si>
-  <si>
-    <t>693/229</t>
-  </si>
-  <si>
-    <t>693/186</t>
-  </si>
-  <si>
-    <t>693/74</t>
-  </si>
-  <si>
-    <t>693/158</t>
-  </si>
-  <si>
-    <t>693/157</t>
-  </si>
-  <si>
-    <t>693/75</t>
-  </si>
-  <si>
-    <t>693/163</t>
-  </si>
-  <si>
-    <t>693/141</t>
-  </si>
-  <si>
-    <t>693/76</t>
-  </si>
-  <si>
-    <t>693/190</t>
-  </si>
-  <si>
-    <t>693/140</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>NOVÁ INVALIDOVNA - Novostavba dvou bytových domů a ubytovacího objektu</t>
+    <t>Smíchov</t>
+  </si>
+  <si>
+    <t>4606/3</t>
+  </si>
+  <si>
+    <t>4745</t>
+  </si>
+  <si>
+    <t>4759/2</t>
+  </si>
+  <si>
+    <t>4761/3</t>
+  </si>
+  <si>
+    <t>4752/1</t>
+  </si>
+  <si>
+    <t>4671/15</t>
+  </si>
+  <si>
+    <t>4671/16</t>
+  </si>
+  <si>
+    <t>4670/5</t>
+  </si>
+  <si>
+    <t>4688/9</t>
+  </si>
+  <si>
+    <t>4752/2</t>
+  </si>
+  <si>
+    <t>4733/10</t>
+  </si>
+  <si>
+    <t>4669</t>
+  </si>
+  <si>
+    <t>4671/14</t>
+  </si>
+  <si>
+    <t>4748/5</t>
+  </si>
+  <si>
+    <t>4761/1</t>
+  </si>
+  <si>
+    <t>4735</t>
+  </si>
+  <si>
+    <t>4733/2</t>
+  </si>
+  <si>
+    <t>4744</t>
+  </si>
+  <si>
+    <t>4757</t>
+  </si>
+  <si>
+    <t>4760</t>
+  </si>
+  <si>
+    <t>4758</t>
+  </si>
+  <si>
+    <t>4759/1</t>
+  </si>
+  <si>
+    <t>4761/2</t>
+  </si>
+  <si>
+    <t>2981</t>
+  </si>
+  <si>
+    <t>10882</t>
+  </si>
+  <si>
+    <t>8093</t>
+  </si>
+  <si>
+    <t>14715</t>
+  </si>
+  <si>
+    <t>5142</t>
+  </si>
+  <si>
+    <t>10881</t>
+  </si>
+  <si>
+    <t>12737</t>
+  </si>
+  <si>
+    <t>14803</t>
+  </si>
+  <si>
+    <t>2938</t>
+  </si>
+  <si>
+    <t>14292</t>
+  </si>
+  <si>
+    <t>2820</t>
+  </si>
+  <si>
+    <t>13890</t>
+  </si>
+  <si>
+    <t>Součková Alena MUDr., - podíl = 1/9</t>
+  </si>
+  <si>
+    <t>Součková Alena MUDr., - podíl = 251181/2160000</t>
+  </si>
+  <si>
+    <t>Součková Alena MUDr., - podíl = 0/1</t>
+  </si>
+  <si>
+    <t>Součková Alena MUDr., - podíl = 3240/27864</t>
   </si>
 </sst>
 </file>
@@ -491,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -534,16 +561,16 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G2">
-        <v>50.09685859</v>
+        <v>50.07024363</v>
       </c>
       <c r="H2">
-        <v>14.46331886</v>
+        <v>14.36401937</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -560,16 +587,16 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G3">
-        <v>50.09707398</v>
+        <v>50.07352709</v>
       </c>
       <c r="H3">
-        <v>14.46374658</v>
+        <v>14.36473681</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -586,16 +613,16 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G4">
-        <v>50.09690494</v>
+        <v>50.0717317</v>
       </c>
       <c r="H4">
-        <v>14.46390335</v>
+        <v>14.36252871</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -612,16 +639,16 @@
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G5">
-        <v>50.09719019</v>
+        <v>50.07004565</v>
       </c>
       <c r="H5">
-        <v>14.46392314</v>
+        <v>14.36325711</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -638,16 +665,16 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G6">
-        <v>50.09718533</v>
+        <v>50.07368348</v>
       </c>
       <c r="H6">
-        <v>14.46416345</v>
+        <v>14.36161547</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -664,16 +691,16 @@
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G7">
-        <v>50.09698222</v>
+        <v>50.0739159</v>
       </c>
       <c r="H7">
-        <v>14.46419218</v>
+        <v>14.37109405</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -690,16 +717,16 @@
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G8">
-        <v>50.09698781</v>
+        <v>50.07412754</v>
       </c>
       <c r="H8">
-        <v>14.46421554</v>
+        <v>14.37121302</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -716,16 +743,16 @@
         <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G9">
-        <v>50.09708465</v>
+        <v>50.07306112</v>
       </c>
       <c r="H9">
-        <v>14.46442557</v>
+        <v>14.37206778</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -745,13 +772,13 @@
         <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G10">
-        <v>50.09702665</v>
+        <v>50.07573047</v>
       </c>
       <c r="H10">
-        <v>14.4644636</v>
+        <v>14.37042542</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -768,16 +795,16 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G11">
-        <v>50.09737867</v>
+        <v>50.07364519</v>
       </c>
       <c r="H11">
-        <v>14.46432457</v>
+        <v>14.3613405</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -794,16 +821,16 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G12">
-        <v>50.09745444</v>
+        <v>50.07350091</v>
       </c>
       <c r="H12">
-        <v>14.46450778</v>
+        <v>14.36926261</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -820,16 +847,16 @@
         <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G13">
-        <v>50.09738917</v>
+        <v>50.07375495</v>
       </c>
       <c r="H13">
-        <v>14.46447146</v>
+        <v>14.37075729</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -846,16 +873,16 @@
         <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G14">
-        <v>50.09720569</v>
+        <v>50.07311911</v>
       </c>
       <c r="H14">
-        <v>14.4645633</v>
+        <v>14.37236644</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -872,16 +899,16 @@
         <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G15">
-        <v>50.09728172</v>
+        <v>50.07334401</v>
       </c>
       <c r="H15">
-        <v>14.46465263</v>
+        <v>14.36139033</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -898,16 +925,16 @@
         <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G16">
-        <v>50.09750857</v>
+        <v>50.07044285</v>
       </c>
       <c r="H16">
-        <v>14.46466371</v>
+        <v>14.36362073</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -924,16 +951,16 @@
         <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G17">
-        <v>50.09745628</v>
+        <v>50.07132229</v>
       </c>
       <c r="H17">
-        <v>14.46470363</v>
+        <v>14.36468044</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -950,16 +977,16 @@
         <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F18" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G18">
-        <v>50.09742068</v>
+        <v>50.07214205</v>
       </c>
       <c r="H18">
-        <v>14.46469611</v>
+        <v>14.36724217</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -976,16 +1003,16 @@
         <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G19">
-        <v>50.09728398</v>
+        <v>50.07310003</v>
       </c>
       <c r="H19">
-        <v>14.46476276</v>
+        <v>14.36511395</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1002,16 +1029,16 @@
         <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G20">
-        <v>50.09716693</v>
+        <v>50.07242751</v>
       </c>
       <c r="H20">
-        <v>14.46502555</v>
+        <v>14.36168674</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1028,16 +1055,16 @@
         <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G21">
-        <v>50.0973429</v>
+        <v>50.07303919</v>
       </c>
       <c r="H21">
-        <v>14.46493389</v>
+        <v>14.36203512</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1054,16 +1081,16 @@
         <v>30</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G22">
-        <v>50.09753611</v>
+        <v>50.07239418</v>
       </c>
       <c r="H22">
-        <v>14.46483405</v>
+        <v>14.3644573</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1080,16 +1107,16 @@
         <v>31</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G23">
-        <v>50.09761448</v>
+        <v>50.0720989</v>
       </c>
       <c r="H23">
-        <v>14.46507977</v>
+        <v>14.36346249</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1106,146 +1133,16 @@
         <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G24">
-        <v>50.09741135</v>
+        <v>50.07071656</v>
       </c>
       <c r="H24">
-        <v>14.46518652</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" t="s">
-        <v>39</v>
-      </c>
-      <c r="G25">
-        <v>50.09687911</v>
-      </c>
-      <c r="H25">
-        <v>14.46568813</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" t="s">
-        <v>39</v>
-      </c>
-      <c r="G26">
-        <v>50.09769743</v>
-      </c>
-      <c r="H26">
-        <v>14.46539688</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" t="s">
-        <v>39</v>
-      </c>
-      <c r="G27">
-        <v>50.09746924</v>
-      </c>
-      <c r="H27">
-        <v>14.46552519</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" t="s">
-        <v>39</v>
-      </c>
-      <c r="G28">
-        <v>50.09737217</v>
-      </c>
-      <c r="H28">
-        <v>14.46591578</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" t="s">
-        <v>39</v>
-      </c>
-      <c r="G29">
-        <v>50.09750687</v>
-      </c>
-      <c r="H29">
-        <v>14.46583574</v>
+        <v>14.36591125</v>
       </c>
     </row>
   </sheetData>

--- a/GIS2/parcely_gps.xlsx
+++ b/GIS2/parcely_gps.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="48">
   <si>
     <t>okres</t>
   </si>
@@ -49,127 +49,115 @@
     <t>lon</t>
   </si>
   <si>
-    <t>Beroun</t>
-  </si>
-  <si>
-    <t>1410/48</t>
-  </si>
-  <si>
-    <t>1410/49</t>
-  </si>
-  <si>
-    <t>1410/52</t>
-  </si>
-  <si>
-    <t>1410/54</t>
-  </si>
-  <si>
-    <t>1410/55</t>
-  </si>
-  <si>
-    <t>1410/56</t>
-  </si>
-  <si>
-    <t>1410/58</t>
-  </si>
-  <si>
-    <t>1410/59</t>
-  </si>
-  <si>
-    <t>1410/60</t>
-  </si>
-  <si>
-    <t>1410/62</t>
-  </si>
-  <si>
-    <t>1410/65</t>
-  </si>
-  <si>
-    <t>1410/66</t>
-  </si>
-  <si>
-    <t>1410/67</t>
-  </si>
-  <si>
-    <t>1410/69</t>
-  </si>
-  <si>
-    <t>1410/70</t>
-  </si>
-  <si>
-    <t>1410/221</t>
-  </si>
-  <si>
-    <t>1410/222</t>
-  </si>
-  <si>
-    <t>1410/223</t>
-  </si>
-  <si>
-    <t>1410/224</t>
-  </si>
-  <si>
-    <t>1410/250</t>
-  </si>
-  <si>
-    <t>2272/6</t>
-  </si>
-  <si>
-    <t>9744 - stavební</t>
-  </si>
-  <si>
-    <t>9744 - komunikace</t>
+    <t>Praha</t>
+  </si>
+  <si>
+    <t>Krč</t>
+  </si>
+  <si>
+    <t>Braník</t>
+  </si>
+  <si>
+    <t>2537/3</t>
+  </si>
+  <si>
+    <t>2543/1</t>
+  </si>
+  <si>
+    <t>2543/15</t>
+  </si>
+  <si>
+    <t>2543/2</t>
+  </si>
+  <si>
+    <t>2543/3</t>
+  </si>
+  <si>
+    <t>2543/4</t>
+  </si>
+  <si>
+    <t>2543/5</t>
+  </si>
+  <si>
+    <t>2543/6</t>
+  </si>
+  <si>
+    <t>2545/2</t>
+  </si>
+  <si>
+    <t>2545/4</t>
+  </si>
+  <si>
+    <t>2545/5</t>
+  </si>
+  <si>
+    <t>2545/6</t>
+  </si>
+  <si>
+    <t>2545/9</t>
+  </si>
+  <si>
+    <t>2547</t>
+  </si>
+  <si>
+    <t>2544/2</t>
+  </si>
+  <si>
+    <t>2545/1</t>
+  </si>
+  <si>
+    <t>2545/3</t>
+  </si>
+  <si>
+    <t>2546/1</t>
+  </si>
+  <si>
+    <t>2546/2</t>
+  </si>
+  <si>
+    <t>2544/1</t>
+  </si>
+  <si>
+    <t>2722/3</t>
+  </si>
+  <si>
+    <t>2722/2</t>
+  </si>
+  <si>
+    <t>2721/2</t>
+  </si>
+  <si>
+    <t>2709/9</t>
+  </si>
+  <si>
+    <t>2709/1</t>
+  </si>
+  <si>
+    <t>551 - Technologická část</t>
+  </si>
+  <si>
+    <t>551 - Farma - Zahradnictví</t>
+  </si>
+  <si>
+    <t>551 - Technologická část (20 147 m2) + Farma - Zahradnictví (28 900 m2)</t>
+  </si>
+  <si>
+    <t>6859 - Technologická část</t>
   </si>
   <si>
     <t>Nezjištěno</t>
   </si>
   <si>
-    <t>19 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>18 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>komunikace</t>
-  </si>
-  <si>
-    <t>14 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>13 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>12 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>3 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>4 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>5 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>1 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>10 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>15 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>6 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>7 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>8 - stavební parcela, ÚP - rozvojová plocha (P.1a), [BI]</t>
-  </si>
-  <si>
-    <t>2 - část stavební parcely, ÚP - rozvojová plocha (P.1a), [BI]</t>
+    <t>VN-D</t>
+  </si>
+  <si>
+    <t>Technologická část</t>
+  </si>
+  <si>
+    <t>Farma - Zahradnictví</t>
+  </si>
+  <si>
+    <t>Technologická část (20 147 m2) + Farma - Zahradnictví (28 900 m2)</t>
   </si>
 </sst>
 </file>
@@ -527,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -570,28 +558,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J2">
-        <v>49.96142232</v>
+        <v>50.0332333</v>
       </c>
       <c r="K2">
-        <v>14.04872413</v>
+        <v>14.44389041</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -599,28 +587,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J3">
-        <v>49.96126498</v>
+        <v>50.03168045</v>
       </c>
       <c r="K3">
-        <v>14.04894084</v>
+        <v>14.43308034</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -628,28 +616,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J4">
-        <v>49.96145504</v>
+        <v>50.03195735</v>
       </c>
       <c r="K4">
-        <v>14.0492681</v>
+        <v>14.43698761</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -657,28 +645,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J5">
-        <v>49.96172354</v>
+        <v>50.03112336</v>
       </c>
       <c r="K5">
-        <v>14.04945876</v>
+        <v>14.43787955</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -686,28 +674,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J6">
-        <v>49.961587</v>
+        <v>50.03125587</v>
       </c>
       <c r="K6">
-        <v>14.04967354</v>
+        <v>14.4364122</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -715,28 +703,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J7">
-        <v>49.96143118</v>
+        <v>50.03189178</v>
       </c>
       <c r="K7">
-        <v>14.04991764</v>
+        <v>14.436296</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -744,28 +732,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J8">
-        <v>49.96156519</v>
+        <v>50.03219068</v>
       </c>
       <c r="K8">
-        <v>14.05054381</v>
+        <v>14.43460981</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -773,28 +761,28 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J9">
-        <v>49.96179899</v>
+        <v>50.03145683</v>
       </c>
       <c r="K9">
-        <v>14.05060319</v>
+        <v>14.4380471</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -802,28 +790,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J10">
-        <v>49.96196644</v>
+        <v>50.03253491</v>
       </c>
       <c r="K10">
-        <v>14.05040255</v>
+        <v>14.43878526</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -831,28 +819,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J11">
-        <v>49.96175486</v>
+        <v>50.03197325</v>
       </c>
       <c r="K11">
-        <v>14.05091818</v>
+        <v>14.43834767</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -860,28 +848,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J12">
-        <v>49.96094623</v>
+        <v>50.03312466</v>
       </c>
       <c r="K12">
-        <v>14.05067618</v>
+        <v>14.44378676</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -889,28 +877,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I13" t="s">
         <v>45</v>
       </c>
       <c r="J13">
-        <v>49.96114076</v>
+        <v>50.03223209</v>
       </c>
       <c r="K13">
-        <v>14.05066414</v>
+        <v>14.43911177</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -918,28 +906,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J14">
-        <v>49.96106062</v>
+        <v>50.03261273</v>
       </c>
       <c r="K14">
-        <v>14.05026413</v>
+        <v>14.44330679</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -947,28 +935,28 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I15" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J15">
-        <v>49.96101452</v>
+        <v>50.0302555</v>
       </c>
       <c r="K15">
-        <v>14.0498421</v>
+        <v>14.44266426</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -976,28 +964,28 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J16">
-        <v>49.96086701</v>
+        <v>50.03142338</v>
       </c>
       <c r="K16">
-        <v>14.04956471</v>
+        <v>14.43827727</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1005,28 +993,28 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J17">
-        <v>49.96208553</v>
+        <v>50.03137313</v>
       </c>
       <c r="K17">
-        <v>14.05020051</v>
+        <v>14.44021301</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1034,28 +1022,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J18">
-        <v>49.96217549</v>
+        <v>50.03199257</v>
       </c>
       <c r="K18">
-        <v>14.0499276</v>
+        <v>14.44133559</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1063,28 +1051,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J19">
-        <v>49.96246331</v>
+        <v>50.02959843</v>
       </c>
       <c r="K19">
-        <v>14.05004797</v>
+        <v>14.44076442</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1092,28 +1080,28 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I20" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J20">
-        <v>49.96251016</v>
+        <v>50.0306601</v>
       </c>
       <c r="K20">
-        <v>14.050186</v>
+        <v>14.44183129</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1121,28 +1109,28 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I21" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J21">
-        <v>49.96143669</v>
+        <v>50.03069151</v>
       </c>
       <c r="K21">
-        <v>14.05049465</v>
+        <v>14.43797263</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1150,28 +1138,156 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F22" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22">
+        <v>50.03230745</v>
+      </c>
+      <c r="K22">
+        <v>14.43052156</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
         <v>35</v>
       </c>
-      <c r="I22" t="s">
+      <c r="E23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23">
+        <v>15512250</v>
+      </c>
+      <c r="H23">
+        <v>2134.321684094662</v>
+      </c>
+      <c r="I23" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23">
+        <v>50.03197742</v>
+      </c>
+      <c r="K23">
+        <v>14.43048125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24">
+        <v>15512250</v>
+      </c>
+      <c r="H24">
+        <v>2134.321684094662</v>
+      </c>
+      <c r="I24" t="s">
+        <v>45</v>
+      </c>
+      <c r="J24">
+        <v>50.03163103</v>
+      </c>
+      <c r="K24">
+        <v>14.4306896</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" t="s">
+        <v>43</v>
+      </c>
+      <c r="I25" t="s">
+        <v>45</v>
+      </c>
+      <c r="J25">
+        <v>50.0314067</v>
+      </c>
+      <c r="K25">
+        <v>14.43073198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
         <v>38</v>
       </c>
-      <c r="J22">
-        <v>49.96204178</v>
-      </c>
-      <c r="K22">
-        <v>14.0508995</v>
+      <c r="E26" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" t="s">
+        <v>43</v>
+      </c>
+      <c r="I26" t="s">
+        <v>45</v>
+      </c>
+      <c r="J26">
+        <v>50.03114744</v>
+      </c>
+      <c r="K26">
+        <v>14.43040958</v>
       </c>
     </row>
   </sheetData>

--- a/GIS2/parcely_gps.xlsx
+++ b/GIS2/parcely_gps.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="86">
   <si>
     <t>okres</t>
   </si>
@@ -49,97 +49,229 @@
     <t>lon</t>
   </si>
   <si>
-    <t>Praha-východ</t>
-  </si>
-  <si>
-    <t>Křížkový Újezdec</t>
-  </si>
-  <si>
-    <t>Sulice</t>
-  </si>
-  <si>
-    <t>Radějovice</t>
-  </si>
-  <si>
-    <t>Velké Popovice</t>
-  </si>
-  <si>
-    <t>834/2</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>68/1</t>
-  </si>
-  <si>
-    <t>874/99</t>
-  </si>
-  <si>
-    <t>874/16</t>
-  </si>
-  <si>
-    <t>874/101</t>
-  </si>
-  <si>
-    <t>675/5</t>
-  </si>
-  <si>
-    <t>418/30</t>
-  </si>
-  <si>
-    <t>301/74</t>
-  </si>
-  <si>
-    <t>69/44</t>
-  </si>
-  <si>
-    <t>V-9802/2024-209</t>
-  </si>
-  <si>
-    <t>V-10317/2024-209</t>
-  </si>
-  <si>
-    <t>V-2687/2025-209</t>
-  </si>
-  <si>
-    <t>V-9676/2024-209</t>
-  </si>
-  <si>
-    <t>V-7112/2024-209</t>
-  </si>
-  <si>
-    <t>V-13792/2023-209</t>
-  </si>
-  <si>
-    <t>V-2373/2023-209</t>
-  </si>
-  <si>
-    <t>V-7451/2026-209</t>
-  </si>
-  <si>
-    <t>V-16868/2025-209</t>
+    <t>Praha</t>
+  </si>
+  <si>
+    <t>Benešov</t>
+  </si>
+  <si>
+    <t>Smíchov</t>
+  </si>
+  <si>
+    <t>Dunávice</t>
+  </si>
+  <si>
+    <t>Netvořice</t>
+  </si>
+  <si>
+    <t>4606/3</t>
+  </si>
+  <si>
+    <t>4745</t>
+  </si>
+  <si>
+    <t>4759/2</t>
+  </si>
+  <si>
+    <t>4761/3</t>
+  </si>
+  <si>
+    <t>4752/1</t>
+  </si>
+  <si>
+    <t>4671/15</t>
+  </si>
+  <si>
+    <t>4671/16</t>
+  </si>
+  <si>
+    <t>4670/5</t>
+  </si>
+  <si>
+    <t>4688/9</t>
+  </si>
+  <si>
+    <t>4752/2</t>
+  </si>
+  <si>
+    <t>4733/10</t>
+  </si>
+  <si>
+    <t>4669</t>
+  </si>
+  <si>
+    <t>4671/14</t>
+  </si>
+  <si>
+    <t>4748/5</t>
+  </si>
+  <si>
+    <t>4761/1</t>
+  </si>
+  <si>
+    <t>4735</t>
+  </si>
+  <si>
+    <t>4733/2</t>
+  </si>
+  <si>
+    <t>4744</t>
+  </si>
+  <si>
+    <t>4757</t>
+  </si>
+  <si>
+    <t>4760</t>
+  </si>
+  <si>
+    <t>4758</t>
+  </si>
+  <si>
+    <t>4759/1</t>
+  </si>
+  <si>
+    <t>4761/2</t>
+  </si>
+  <si>
+    <t>391/5</t>
+  </si>
+  <si>
+    <t>391/1</t>
+  </si>
+  <si>
+    <t>394</t>
+  </si>
+  <si>
+    <t>4671/1</t>
+  </si>
+  <si>
+    <t>4671/2</t>
+  </si>
+  <si>
+    <t>4747</t>
+  </si>
+  <si>
+    <t>4671/7</t>
+  </si>
+  <si>
+    <t>4671/9</t>
+  </si>
+  <si>
+    <t>4671/10</t>
+  </si>
+  <si>
+    <t>4671/8</t>
+  </si>
+  <si>
+    <t>4707</t>
+  </si>
+  <si>
+    <t>4748/6</t>
+  </si>
+  <si>
+    <t>2981</t>
+  </si>
+  <si>
+    <t>10882</t>
+  </si>
+  <si>
+    <t>8093</t>
+  </si>
+  <si>
+    <t>14715</t>
+  </si>
+  <si>
+    <t>5142</t>
+  </si>
+  <si>
+    <t>10881</t>
+  </si>
+  <si>
+    <t>12737</t>
+  </si>
+  <si>
+    <t>14803</t>
+  </si>
+  <si>
+    <t>2938</t>
+  </si>
+  <si>
+    <t>14292</t>
+  </si>
+  <si>
+    <t>2820</t>
+  </si>
+  <si>
+    <t>13890</t>
+  </si>
+  <si>
+    <t>581</t>
+  </si>
+  <si>
+    <t>569</t>
+  </si>
+  <si>
+    <t>18427</t>
+  </si>
+  <si>
+    <t>18426</t>
+  </si>
+  <si>
+    <t>14665</t>
+  </si>
+  <si>
+    <t>18438</t>
+  </si>
+  <si>
+    <t>18425</t>
+  </si>
+  <si>
+    <t>OB</t>
+  </si>
+  <si>
+    <t>NL</t>
+  </si>
+  <si>
+    <t>PZO</t>
+  </si>
+  <si>
+    <t>LR</t>
+  </si>
+  <si>
+    <t>ZMK</t>
+  </si>
+  <si>
+    <t>S4</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>SO1</t>
   </si>
   <si>
     <t>Nezjištěno</t>
   </si>
   <si>
-    <t>OV</t>
-  </si>
-  <si>
-    <t>SV - návrh</t>
-  </si>
-  <si>
-    <t>SV, SV - návrh</t>
-  </si>
-  <si>
-    <t>BI</t>
-  </si>
-  <si>
-    <t>BI - návrh</t>
-  </si>
-  <si>
-    <t>SV</t>
+    <t>Součková Alena MUDr., - podíl = 1/9</t>
+  </si>
+  <si>
+    <t>Součková Alena MUDr., - podíl = 251181/2160000</t>
+  </si>
+  <si>
+    <t>Součková Alena MUDr., - podíl = 0/1</t>
+  </si>
+  <si>
+    <t>Součková Alena MUDr., - podíl = 3240/27864</t>
+  </si>
+  <si>
+    <t>Součková Alena MUDr., - podíl = 358/2909 (1790/14545)</t>
+  </si>
+  <si>
+    <t>Součková Alena MUDr., - podíl = 17771/139320</t>
+  </si>
+  <si>
+    <t>Součková Alena MUDr., - podíl = 1/24</t>
   </si>
 </sst>
 </file>
@@ -497,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -540,34 +672,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="G2">
-        <v>11500000</v>
+        <v>3404859</v>
       </c>
       <c r="H2">
-        <v>6857.483601669648</v>
+        <v>22.57609553299694</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="J2">
-        <v>49.93232319</v>
+        <v>50.07024363</v>
       </c>
       <c r="K2">
-        <v>14.58853534</v>
+        <v>14.36401937</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -575,34 +707,34 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="G3">
-        <v>10951200</v>
+        <v>3404859</v>
       </c>
       <c r="H3">
-        <v>1300.926585887384</v>
+        <v>22.57609553299694</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J3">
-        <v>49.93135665</v>
+        <v>50.07352709</v>
       </c>
       <c r="K3">
-        <v>14.58735302</v>
+        <v>14.36473681</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -610,34 +742,34 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="G4">
-        <v>10951200</v>
+        <v>3404859</v>
       </c>
       <c r="H4">
-        <v>1300.926585887384</v>
+        <v>22.57609553299694</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J4">
-        <v>49.93157804</v>
+        <v>50.0717317</v>
       </c>
       <c r="K4">
-        <v>14.58699047</v>
+        <v>14.36252871</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -648,25 +780,31 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>73</v>
+      </c>
+      <c r="G5">
+        <v>3404859</v>
+      </c>
+      <c r="H5">
+        <v>22.57609553299694</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="J5">
-        <v>49.9245767</v>
+        <v>50.07004565</v>
       </c>
       <c r="K5">
-        <v>14.5784093</v>
+        <v>14.36325711</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -677,31 +815,31 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="G6">
-        <v>11800000</v>
+        <v>3404859</v>
       </c>
       <c r="H6">
-        <v>8644.688644688646</v>
+        <v>22.57609553299694</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="J6">
-        <v>49.92299123</v>
+        <v>50.07368348</v>
       </c>
       <c r="K6">
-        <v>14.57859653</v>
+        <v>14.36161547</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -712,31 +850,31 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G7">
-        <v>8700000</v>
+        <v>3404859</v>
       </c>
       <c r="H7">
-        <v>6910.246227164416</v>
+        <v>22.57609553299694</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="J7">
-        <v>49.92488601</v>
+        <v>50.0739159</v>
       </c>
       <c r="K7">
-        <v>14.57904825</v>
+        <v>14.37109405</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -747,31 +885,31 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G8">
-        <v>9300000</v>
+        <v>3404859</v>
       </c>
       <c r="H8">
-        <v>7868.020304568528</v>
+        <v>22.57609553299694</v>
       </c>
       <c r="I8" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="J8">
-        <v>49.93311481</v>
+        <v>50.07412754</v>
       </c>
       <c r="K8">
-        <v>14.55433262</v>
+        <v>14.37121302</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -782,31 +920,31 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="G9">
-        <v>7540000</v>
+        <v>3404859</v>
       </c>
       <c r="H9">
-        <v>6210.873146622735</v>
+        <v>22.57609553299694</v>
       </c>
       <c r="I9" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="J9">
-        <v>49.92191298</v>
+        <v>50.07306112</v>
       </c>
       <c r="K9">
-        <v>14.56296323</v>
+        <v>14.37206778</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -814,28 +952,34 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>70</v>
+      </c>
+      <c r="G10">
+        <v>3404859</v>
+      </c>
+      <c r="H10">
+        <v>22.57609553299694</v>
       </c>
       <c r="I10" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="J10">
-        <v>49.9475704</v>
+        <v>50.07573047</v>
       </c>
       <c r="K10">
-        <v>14.56075656</v>
+        <v>14.37042542</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -843,28 +987,885 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
       </c>
       <c r="E11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11">
+        <v>3404859</v>
+      </c>
+      <c r="H11">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11">
+        <v>50.07364519</v>
+      </c>
+      <c r="K11">
+        <v>14.3613405</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12">
+        <v>18000000</v>
+      </c>
+      <c r="H12">
+        <v>7981.199840376003</v>
+      </c>
+      <c r="I12" t="s">
+        <v>79</v>
+      </c>
+      <c r="J12">
+        <v>50.07350091</v>
+      </c>
+      <c r="K12">
+        <v>14.36926261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13">
+        <v>3404859</v>
+      </c>
+      <c r="H13">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13">
+        <v>50.07375495</v>
+      </c>
+      <c r="K13">
+        <v>14.37075729</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14">
+        <v>3404859</v>
+      </c>
+      <c r="H14">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I14" t="s">
+        <v>81</v>
+      </c>
+      <c r="J14">
+        <v>50.07311911</v>
+      </c>
+      <c r="K14">
+        <v>14.37236644</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15">
+        <v>3404859</v>
+      </c>
+      <c r="H15">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15">
+        <v>50.07334401</v>
+      </c>
+      <c r="K15">
+        <v>14.36139033</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16">
+        <v>3404859</v>
+      </c>
+      <c r="H16">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I16" t="s">
+        <v>82</v>
+      </c>
+      <c r="J16">
+        <v>50.07044285</v>
+      </c>
+      <c r="K16">
+        <v>14.36362073</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17">
+        <v>3404859</v>
+      </c>
+      <c r="H17">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I17" t="s">
+        <v>79</v>
+      </c>
+      <c r="J17">
+        <v>50.07132229</v>
+      </c>
+      <c r="K17">
+        <v>14.36468044</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18">
+        <v>3404859</v>
+      </c>
+      <c r="H18">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I18" t="s">
+        <v>79</v>
+      </c>
+      <c r="J18">
+        <v>50.07214205</v>
+      </c>
+      <c r="K18">
+        <v>14.36724217</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19">
+        <v>3404859</v>
+      </c>
+      <c r="H19">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I19" t="s">
+        <v>79</v>
+      </c>
+      <c r="J19">
+        <v>50.07310003</v>
+      </c>
+      <c r="K19">
+        <v>14.36511395</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
         <v>34</v>
       </c>
-      <c r="F11" t="s">
+      <c r="E20" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" t="s">
+        <v>73</v>
+      </c>
+      <c r="G20">
+        <v>3404859</v>
+      </c>
+      <c r="H20">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I20" t="s">
+        <v>79</v>
+      </c>
+      <c r="J20">
+        <v>50.07242751</v>
+      </c>
+      <c r="K20">
+        <v>14.36168674</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
         <v>35</v>
       </c>
-      <c r="I11" t="s">
+      <c r="E21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21">
+        <v>3404859</v>
+      </c>
+      <c r="H21">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21">
+        <v>50.07303919</v>
+      </c>
+      <c r="K21">
+        <v>14.36203512</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22">
+        <v>3404859</v>
+      </c>
+      <c r="H22">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I22" t="s">
+        <v>79</v>
+      </c>
+      <c r="J22">
+        <v>50.07239418</v>
+      </c>
+      <c r="K22">
+        <v>14.3644573</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23">
+        <v>3404859</v>
+      </c>
+      <c r="H23">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I23" t="s">
+        <v>79</v>
+      </c>
+      <c r="J23">
+        <v>50.0720989</v>
+      </c>
+      <c r="K23">
+        <v>14.36346249</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24">
+        <v>3404859</v>
+      </c>
+      <c r="H24">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I24" t="s">
+        <v>79</v>
+      </c>
+      <c r="J24">
+        <v>50.07071656</v>
+      </c>
+      <c r="K24">
+        <v>14.36591125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
         <v>39</v>
       </c>
-      <c r="J11">
-        <v>49.9214269</v>
-      </c>
-      <c r="K11">
-        <v>14.6262824</v>
+      <c r="E25" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" t="s">
+        <v>78</v>
+      </c>
+      <c r="I25" t="s">
+        <v>83</v>
+      </c>
+      <c r="J25">
+        <v>49.81697204</v>
+      </c>
+      <c r="K25">
+        <v>14.55184397</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" t="s">
+        <v>78</v>
+      </c>
+      <c r="I26" t="s">
+        <v>84</v>
+      </c>
+      <c r="J26">
+        <v>49.81746623</v>
+      </c>
+      <c r="K26">
+        <v>14.55176981</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" t="s">
+        <v>78</v>
+      </c>
+      <c r="I27" t="s">
+        <v>84</v>
+      </c>
+      <c r="J27">
+        <v>49.81663439</v>
+      </c>
+      <c r="K27">
+        <v>14.55261829</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" t="s">
+        <v>74</v>
+      </c>
+      <c r="G28">
+        <v>3404859</v>
+      </c>
+      <c r="H28">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I28" t="s">
+        <v>79</v>
+      </c>
+      <c r="J28">
+        <v>50.07363255</v>
+      </c>
+      <c r="K28">
+        <v>14.37077104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29">
+        <v>3404859</v>
+      </c>
+      <c r="H29">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I29" t="s">
+        <v>79</v>
+      </c>
+      <c r="J29">
+        <v>50.07387411</v>
+      </c>
+      <c r="K29">
+        <v>14.37081828</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30">
+        <v>3404859</v>
+      </c>
+      <c r="H30">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I30" t="s">
+        <v>79</v>
+      </c>
+      <c r="J30">
+        <v>50.07405197</v>
+      </c>
+      <c r="K30">
+        <v>14.36397208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" t="s">
+        <v>66</v>
+      </c>
+      <c r="F31" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31">
+        <v>3404859</v>
+      </c>
+      <c r="H31">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I31" t="s">
+        <v>79</v>
+      </c>
+      <c r="J31">
+        <v>50.07415479</v>
+      </c>
+      <c r="K31">
+        <v>14.3710949</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" t="s">
+        <v>74</v>
+      </c>
+      <c r="G32">
+        <v>3404859</v>
+      </c>
+      <c r="H32">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I32" t="s">
+        <v>79</v>
+      </c>
+      <c r="J32">
+        <v>50.07361921</v>
+      </c>
+      <c r="K32">
+        <v>14.37100252</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" t="s">
+        <v>66</v>
+      </c>
+      <c r="F33" t="s">
+        <v>70</v>
+      </c>
+      <c r="G33">
+        <v>3404859</v>
+      </c>
+      <c r="H33">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I33" t="s">
+        <v>79</v>
+      </c>
+      <c r="J33">
+        <v>50.07316263</v>
+      </c>
+      <c r="K33">
+        <v>14.37200282</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" t="s">
+        <v>67</v>
+      </c>
+      <c r="F34" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34" t="s">
+        <v>85</v>
+      </c>
+      <c r="J34">
+        <v>50.07375822</v>
+      </c>
+      <c r="K34">
+        <v>14.37088267</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" t="s">
+        <v>68</v>
+      </c>
+      <c r="F35" t="s">
+        <v>74</v>
+      </c>
+      <c r="G35">
+        <v>3404859</v>
+      </c>
+      <c r="H35">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I35" t="s">
+        <v>79</v>
+      </c>
+      <c r="J35">
+        <v>50.07450949</v>
+      </c>
+      <c r="K35">
+        <v>14.37155053</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36" t="s">
+        <v>73</v>
+      </c>
+      <c r="G36">
+        <v>3404859</v>
+      </c>
+      <c r="H36">
+        <v>22.57609553299694</v>
+      </c>
+      <c r="I36" t="s">
+        <v>79</v>
+      </c>
+      <c r="J36">
+        <v>50.07441871</v>
+      </c>
+      <c r="K36">
+        <v>14.3639612</v>
       </c>
     </row>
   </sheetData>
